--- a/Chinese_Olfactory_Corpus_and_Annotation_Dataset/Manually-annotated text corpus.xlsx
+++ b/Chinese_Olfactory_Corpus_and_Annotation_Dataset/Manually-annotated text corpus.xlsx
@@ -263,6 +263,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>花的芳香油的气味和人鼻腔内的嗅觉细胞相接触后，会通过嗅觉神经传递到大脑皮层，产生</t>
     </r>
     <r>
